--- a/data/mgiliberti.xlsx
+++ b/data/mgiliberti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{A091660E-5A97-41A8-B730-FDB855044DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3155A14A-DEA1-41F3-80E6-DD11C819E89C}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{A091660E-5A97-41A8-B730-FDB855044DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EE89FA0-568F-42BD-A73C-03AAC6BC7786}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="16">
   <si>
     <t>INV7</t>
   </si>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -3015,35 +3015,219 @@
         <v>15</v>
       </c>
       <c r="D56" s="4">
-        <f t="shared" ref="D56" si="75">+D55+E55+K55-F55</f>
+        <f t="shared" ref="D56:D60" si="75">+D55+E55+K55-F55</f>
         <v>40833.055</v>
+      </c>
+      <c r="G56" s="4">
+        <v>571.66</v>
       </c>
       <c r="H56" s="5">
         <f t="shared" si="69"/>
-        <v>34258.94999999999</v>
+        <v>34830.609999999993</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>57.165999999999997</v>
       </c>
       <c r="J56" s="5">
         <f t="shared" si="6"/>
-        <v>3425.8950000000013</v>
+        <v>3483.0610000000015</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>514.49399999999991</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="72"/>
-        <v>30833.055000000015</v>
+        <v>31347.549000000014</v>
       </c>
       <c r="M56" s="5">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>17.149799999999995</v>
       </c>
       <c r="N56" s="6">
         <f t="shared" si="74"/>
+        <v>1.3999932162802904E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>45901</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="4">
+        <f t="shared" si="75"/>
+        <v>41347.548999999999</v>
+      </c>
+      <c r="G57" s="4">
+        <v>950.99</v>
+      </c>
+      <c r="H57" s="5">
+        <f t="shared" ref="H57:H60" si="76">+H56+G57</f>
+        <v>35781.599999999991</v>
+      </c>
+      <c r="I57" s="5">
+        <f t="shared" ref="I57:I60" si="77">+G57*0.1</f>
+        <v>95.099000000000004</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" ref="J57:J60" si="78">+J56+I57</f>
+        <v>3578.1600000000017</v>
+      </c>
+      <c r="K57" s="5">
+        <f t="shared" ref="K57:K60" si="79">+G57-I57</f>
+        <v>855.89099999999996</v>
+      </c>
+      <c r="L57" s="5">
+        <f t="shared" ref="L57:L60" si="80">+L56+K57</f>
+        <v>32203.440000000013</v>
+      </c>
+      <c r="M57" s="5">
+        <f t="shared" ref="M57:M60" si="81">+K57/30</f>
+        <v>28.529699999999998</v>
+      </c>
+      <c r="N57" s="6">
+        <f t="shared" ref="N57:N60" si="82">+G57/D57</f>
+        <v>2.2999912280169257E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>45931</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="4">
+        <f t="shared" si="75"/>
+        <v>42203.44</v>
+      </c>
+      <c r="G58" s="4">
+        <v>886.27</v>
+      </c>
+      <c r="H58" s="5">
+        <f t="shared" si="76"/>
+        <v>36667.869999999988</v>
+      </c>
+      <c r="I58" s="5">
+        <f t="shared" si="77"/>
+        <v>88.62700000000001</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="78"/>
+        <v>3666.7870000000016</v>
+      </c>
+      <c r="K58" s="5">
+        <f t="shared" si="79"/>
+        <v>797.64300000000003</v>
+      </c>
+      <c r="L58" s="5">
+        <f t="shared" si="80"/>
+        <v>33001.083000000013</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" si="81"/>
+        <v>26.588100000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <f t="shared" si="82"/>
+        <v>2.0999946923757871E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <v>45962</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="4">
+        <f t="shared" si="75"/>
+        <v>43001.082999999999</v>
+      </c>
+      <c r="G59" s="4">
+        <v>1548.04</v>
+      </c>
+      <c r="H59" s="5">
+        <f t="shared" si="76"/>
+        <v>38215.909999999989</v>
+      </c>
+      <c r="I59" s="5">
+        <f t="shared" si="77"/>
+        <v>154.804</v>
+      </c>
+      <c r="J59" s="5">
+        <f t="shared" si="78"/>
+        <v>3821.5910000000017</v>
+      </c>
+      <c r="K59" s="5">
+        <f t="shared" si="79"/>
+        <v>1393.2359999999999</v>
+      </c>
+      <c r="L59" s="5">
+        <f t="shared" si="80"/>
+        <v>34394.31900000001</v>
+      </c>
+      <c r="M59" s="5">
+        <f t="shared" si="81"/>
+        <v>46.441199999999995</v>
+      </c>
+      <c r="N59" s="6">
+        <f t="shared" si="82"/>
+        <v>3.6000023534290986E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>45992</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="4">
+        <f t="shared" si="75"/>
+        <v>44394.318999999996</v>
+      </c>
+      <c r="H60" s="5">
+        <f t="shared" si="76"/>
+        <v>38215.909999999989</v>
+      </c>
+      <c r="I60" s="5">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="78"/>
+        <v>3821.5910000000017</v>
+      </c>
+      <c r="K60" s="5">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="5">
+        <f t="shared" si="80"/>
+        <v>34394.31900000001</v>
+      </c>
+      <c r="M60" s="5">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="6">
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
     </row>

--- a/data/mgiliberti.xlsx
+++ b/data/mgiliberti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAAE562-6D2B-48EA-82FB-AE72993745AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{7EAAE562-6D2B-48EA-82FB-AE72993745AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{538B9816-CF1F-4680-9C37-7544CA7B23FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="16">
   <si>
     <t>INV7</t>
   </si>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -3341,33 +3341,174 @@
         <f t="shared" si="83"/>
         <v>46644.948999999993</v>
       </c>
+      <c r="G63" s="4">
+        <v>603.89</v>
+      </c>
       <c r="H63" s="5">
         <f t="shared" si="84"/>
-        <v>40716.609999999986</v>
+        <v>41320.499999999985</v>
       </c>
       <c r="I63" s="5">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>60.389000000000003</v>
       </c>
       <c r="J63" s="5">
         <f t="shared" si="86"/>
-        <v>4071.6610000000014</v>
+        <v>4132.0500000000011</v>
       </c>
       <c r="K63" s="5">
         <f t="shared" si="87"/>
-        <v>0</v>
+        <v>543.50099999999998</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" si="88"/>
-        <v>36644.949000000008</v>
+        <v>37188.450000000004</v>
       </c>
       <c r="M63" s="5">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>18.116699999999998</v>
       </c>
       <c r="N63" s="6">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>1.2946525035325906E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="4">
+        <f t="shared" ref="D64:D66" si="91">+D63+E63+K63-F63</f>
+        <v>47188.44999999999</v>
+      </c>
+      <c r="G64" s="4">
+        <v>317.25</v>
+      </c>
+      <c r="H64" s="5">
+        <f t="shared" ref="H64:H66" si="92">+H63+G64</f>
+        <v>41637.749999999985</v>
+      </c>
+      <c r="I64" s="5">
+        <f t="shared" ref="I64:I66" si="93">+G64*0.1</f>
+        <v>31.725000000000001</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" ref="J64:J66" si="94">+J63+I64</f>
+        <v>4163.7750000000015</v>
+      </c>
+      <c r="K64" s="5">
+        <f t="shared" ref="K64:K66" si="95">+G64-I64</f>
+        <v>285.52499999999998</v>
+      </c>
+      <c r="L64" s="5">
+        <f t="shared" ref="L64:L66" si="96">+L63+K64</f>
+        <v>37473.975000000006</v>
+      </c>
+      <c r="M64" s="5">
+        <f t="shared" ref="M64:M66" si="97">+K64/30</f>
+        <v>9.5175000000000001</v>
+      </c>
+      <c r="N64" s="6">
+        <f t="shared" ref="N64:N66" si="98">+G64/D64</f>
+        <v>6.7230434566085571E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="4">
+        <f t="shared" si="91"/>
+        <v>47473.974999999991</v>
+      </c>
+      <c r="G65" s="4">
+        <v>1130.1099999999999</v>
+      </c>
+      <c r="H65" s="5">
+        <f t="shared" si="92"/>
+        <v>42767.859999999986</v>
+      </c>
+      <c r="I65" s="5">
+        <f t="shared" si="93"/>
+        <v>113.011</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="94"/>
+        <v>4276.7860000000019</v>
+      </c>
+      <c r="K65" s="5">
+        <f t="shared" si="95"/>
+        <v>1017.0989999999999</v>
+      </c>
+      <c r="L65" s="5">
+        <f t="shared" si="96"/>
+        <v>38491.074000000008</v>
+      </c>
+      <c r="M65" s="5">
+        <f t="shared" si="97"/>
+        <v>33.903299999999994</v>
+      </c>
+      <c r="N65" s="6">
+        <f t="shared" si="98"/>
+        <v>2.3804832015857112E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="4">
+        <f t="shared" si="91"/>
+        <v>48491.073999999993</v>
+      </c>
+      <c r="G66" s="4">
+        <v>884.69</v>
+      </c>
+      <c r="H66" s="5">
+        <f t="shared" si="92"/>
+        <v>43652.549999999988</v>
+      </c>
+      <c r="I66" s="5">
+        <f t="shared" si="93"/>
+        <v>88.469000000000008</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="94"/>
+        <v>4365.2550000000019</v>
+      </c>
+      <c r="K66" s="5">
+        <f t="shared" si="95"/>
+        <v>796.221</v>
+      </c>
+      <c r="L66" s="5">
+        <f t="shared" si="96"/>
+        <v>39287.295000000006</v>
+      </c>
+      <c r="M66" s="5">
+        <f t="shared" si="97"/>
+        <v>26.540700000000001</v>
+      </c>
+      <c r="N66" s="6">
+        <f t="shared" si="98"/>
+        <v>1.8244388647692154E-2</v>
       </c>
     </row>
   </sheetData>
